--- a/config/yunying/collectcard.xlsx
+++ b/config/yunying/collectcard.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="collectcard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="collectcard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1241,16 +1241,14 @@
           <t>18001</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>(初チャージ獲得)</t>
+          <t>（获得第一次充值）</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1295,16 +1293,14 @@
           <t>18001</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>222</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>(V12クリアでパック獲得)</t>
+          <t>（V12通关获得包）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1349,16 +1345,14 @@
           <t>18001</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>(ログイン2日目で獲得)</t>
+          <t>（登录后第2天获得）</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1403,16 +1397,14 @@
           <t>18001</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>(ログイン3日目で獲得)</t>
+          <t>（登录第3天获得）</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1457,16 +1449,14 @@
           <t>18001</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>322</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>(ガチャで獲得)</t>
+          <t>（通过扭蛋获得）</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1511,16 +1501,14 @@
           <t>18001</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>272</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>(ガチャで獲得)</t>
+          <t>（通过扭蛋获得）</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1565,16 +1553,14 @@
           <t>18001</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>(毎日割引で獲得)</t>
+          <t>（每日折扣）</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1619,16 +1605,14 @@
           <t>18001</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>352</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>(ガチャで獲得)</t>
+          <t>（通过扭蛋获得）</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
